--- a/測試工單與圖片/BODA工單_brand_star_mega_zj_1787896948520.xlsx
+++ b/測試工單與圖片/BODA工單_brand_star_mega_zj_1787896948520.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF4B053-5B9D-47C6-97C5-ACF482DD1148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF77DEF-318E-43CB-8FD3-4A42D5BB195A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工單總覽" sheetId="1" r:id="rId1"/>
@@ -1037,7 +1037,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="484">
   <si>
     <t>BODA 工單總覽</t>
   </si>
@@ -2408,10 +2408,6 @@
   </si>
   <si>
     <t>兩</t>
-  </si>
-  <si>
-    <t>滿200送20</t>
-    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>SAMPO 640X360-Photoroom.png</t>
@@ -3057,7 +3053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3116,15 +3112,70 @@
     <xf numFmtId="178" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3133,65 +3184,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3199,6 +3199,34 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="110">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3252,8 +3280,322 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF008000"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3412,78 +3754,6 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF008000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF008000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <color rgb="FFCC0000"/>
       </font>
       <fill>
@@ -3563,100 +3833,6 @@
         <b/>
         <color rgb="FF008000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF008000"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9EAD3"/>
@@ -3671,182 +3847,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF008000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF008000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF008000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFCC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF008000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4024,11 +4024,11 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF008000"/>
+        <color rgb="FFCC0000"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
+          <fgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4046,11 +4046,11 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FFCC0000"/>
+        <color rgb="FF008000"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
+          <fgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5007,35 +5007,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="44">
         <f>IFERROR(VLOOKUP(B3,設定!$A$2:$B$12,2,FALSE),0)</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="24"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="44"/>
       <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
@@ -5047,18 +5047,18 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
@@ -5070,109 +5070,109 @@
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
+      <c r="B5" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="23"/>
+      <c r="F5" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="34"/>
       <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="3">
         <f>SUM(C19:C30)+7</f>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
+      <c r="B6" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
+      <c r="F6" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
+      <c r="B7" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
+      <c r="B11" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
       <c r="I11" s="6" t="str">
         <f>IF(B11="","",IF(LENB(B11)/2&lt;=9,"OK","超過"))</f>
         <v/>
@@ -5182,19 +5182,19 @@
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
+      <c r="B12" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
       <c r="I12" s="6" t="str">
         <f>IF(B12="","",IF(LENB(B12)/2&lt;=8,"OK","超過"))</f>
         <v/>
@@ -5204,19 +5204,19 @@
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
+      <c r="B13" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
       <c r="I13" s="6" t="str">
         <f>IF(B13="","",IF(LENB(B13)/2&lt;=7,"OK","超過"))</f>
         <v/>
@@ -5226,19 +5226,19 @@
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="B14" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="6" t="str">
         <f>IF(B14="","",IF(LENB(B14)/2&lt;=14,"OK","超過"))</f>
         <v/>
@@ -5248,36 +5248,36 @@
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
+      <c r="B15" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="6" t="str">
         <f>IF(B15="","",IF(LENB(B15)/2&lt;=2,"OK","超過"))</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
     </row>
     <row r="18" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -5311,419 +5311,419 @@
     <row r="19" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),1),"")</f>
-        <v/>
+        <v>DDCard</v>
       </c>
       <c r="B19" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),1),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="8" t="str">
+        <v>預設</v>
+      </c>
+      <c r="C19" s="8">
         <f t="shared" ref="C19:C30" si="0">IF(A19="","",IF(B19="預設",1,0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D19" s="9" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>531×792</v>
       </c>
       <c r="E19" s="9" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG</v>
       </c>
       <c r="F19" s="10" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>品牌名≤9；主標≤8；副標≤7；日期/警語≤14</v>
       </c>
       <c r="G19" s="10" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>LOGO、商品圖；CTA 依版型</v>
       </c>
       <c r="H19" s="10" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>ddcard方logo／ddcard橫logo</v>
       </c>
       <c r="I19" s="6" t="str">
         <f t="shared" ref="I19:I30" si="1">IF(A19="","",IF(C19=0,"未選",IF(H19="尚未提供版型","缺版型","待製作")))</f>
-        <v/>
+        <v>待製作</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),2),"")</f>
-        <v/>
+        <v>HBN</v>
       </c>
       <c r="B20" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),2),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="8" t="str">
+        <v>預設</v>
+      </c>
+      <c r="C20" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D20" s="9" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>1200×360</v>
       </c>
       <c r="E20" s="9" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG</v>
       </c>
       <c r="F20" s="10" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>品牌名≤9；主標≤8；副標≤7；日期/警語≤14</v>
       </c>
       <c r="G20" s="10" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>橫式或方形 LOGO 版</v>
       </c>
       <c r="H20" s="10" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>HBN_橫式LOGO／HBN_方式LOGO</v>
       </c>
       <c r="I20" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>待製作</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),3),"")</f>
-        <v/>
+        <v>活動總覽</v>
       </c>
       <c r="B21" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),3),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="8" t="str">
+        <v>預設</v>
+      </c>
+      <c r="C21" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D21" s="9" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>依活動規格</v>
       </c>
       <c r="E21" s="9" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG/PNG</v>
       </c>
       <c r="F21" s="10" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>依活動需求</v>
       </c>
       <c r="G21" s="10" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>目前系統尚未提供可編輯版型</v>
       </c>
       <c r="H21" s="10" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>尚未提供版型</v>
       </c>
       <c r="I21" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>缺版型</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),4),"")</f>
-        <v/>
+        <v>首頁LOGO牆</v>
       </c>
       <c r="B22" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),4),"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="8" t="str">
+        <v>預設</v>
+      </c>
+      <c r="C22" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D22" s="9" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>依活動規格</v>
       </c>
       <c r="E22" s="9" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG/PNG</v>
       </c>
       <c r="F22" s="10" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>LOGO 依活動規範</v>
       </c>
       <c r="G22" s="10" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>目前系統尚未提供可編輯版型</v>
       </c>
       <c r="H22" s="10" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>尚未提供版型</v>
       </c>
       <c r="I22" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>缺版型</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),5),"")</f>
-        <v/>
+        <v>AR</v>
       </c>
       <c r="B23" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),5),"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="8" t="str">
+        <v>預設</v>
+      </c>
+      <c r="C23" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D23" s="9" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>100×100（依規範）</v>
       </c>
       <c r="E23" s="9" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG/PNG</v>
       </c>
       <c r="F23" s="10" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>文案≤6 或 LOGO；2擇1</v>
       </c>
       <c r="G23" s="10" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>目前系統尚未提供可編輯版型</v>
       </c>
       <c r="H23" s="10" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>尚未提供版型</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>缺版型</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),6),"")</f>
-        <v/>
+        <v>FB_Post</v>
       </c>
       <c r="B24" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),6),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="8" t="str">
+        <v>預設</v>
+      </c>
+      <c r="C24" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D24" s="9" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>1200×630</v>
       </c>
       <c r="E24" s="9" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG</v>
       </c>
       <c r="F24" s="10" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>品牌名≤9；主標≤8；副標≤7；日期/警語≤14</v>
       </c>
       <c r="G24" s="10" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>方 LOGO／橫 LOGO</v>
       </c>
       <c r="H24" s="10" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>FB_POST_方LOGO／FB_POST_橫LOGO</v>
       </c>
       <c r="I24" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>待製作</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),7),"")</f>
-        <v/>
+        <v>AMS BN</v>
       </c>
       <c r="B25" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),7),"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="8" t="str">
+        <v>預設</v>
+      </c>
+      <c r="C25" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D25" s="9" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>1077×264（依規範）</v>
       </c>
       <c r="E25" s="9" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG</v>
       </c>
       <c r="F25" s="10" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>依 AMS 規格</v>
       </c>
       <c r="G25" s="10" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>目前系統尚未提供可編輯版型</v>
       </c>
       <c r="H25" s="10" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>尚未提供版型</v>
       </c>
       <c r="I25" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>缺版型</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),8),"")</f>
-        <v/>
+        <v>Coin_page</v>
       </c>
       <c r="B26" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),8),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="8" t="str">
+        <v>選配</v>
+      </c>
+      <c r="C26" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D26" s="9" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>1200×391</v>
       </c>
       <c r="E26" s="9" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG</v>
       </c>
       <c r="F26" s="10" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>品牌名≤9；主標≤8；副標≤7；日期/警語≤14</v>
       </c>
       <c r="G26" s="10" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>方 LOGO／橫 LOGO</v>
       </c>
       <c r="H26" s="10" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>Coin_pageBN_APP方LOGO／Coin_pageBN_APP橫LOGO</v>
       </c>
       <c r="I26" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>未選</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),9),"")</f>
-        <v/>
+        <v>IG</v>
       </c>
       <c r="B27" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),9),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="8" t="str">
+        <v>選配</v>
+      </c>
+      <c r="C27" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D27" s="9" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>900×1600</v>
       </c>
       <c r="E27" s="9" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG</v>
       </c>
       <c r="F27" s="10" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>品牌名≤9；主標≤8；副標≤7；日期/警語≤14</v>
       </c>
       <c r="G27" s="10" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>方 LOGO／橫 LOGO</v>
       </c>
       <c r="H27" s="10" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>IG方logo排版／IG橫logo排版</v>
       </c>
       <c r="I27" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>未選</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),10),"")</f>
-        <v/>
+        <v>SearchIcon</v>
       </c>
       <c r="B28" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),10),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="8" t="str">
+        <v>選配</v>
+      </c>
+      <c r="C28" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D28" s="9" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>120×120＋84×84</v>
       </c>
       <c r="E28" s="9" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>PNG</v>
       </c>
       <c r="F28" s="10" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>ICON 文案≤2；或 LOGO／商品圖</v>
       </c>
       <c r="G28" s="10" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>120×120 建議 &lt;50KB，另輸出 84×84</v>
       </c>
       <c r="H28" s="10" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>SearchICON_LOGO／PRODUCT／TEXT</v>
       </c>
       <c r="I28" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>未選</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="str">
         <f>IFERROR(INDEX(設定!$C$2:$N$12,MATCH($B$3,設定!$A$2:$A$12,0),11),"")</f>
-        <v/>
+        <v>SearchImage</v>
       </c>
       <c r="B29" s="7" t="str">
         <f>IFERROR(INDEX(設定!$O$2:$Z$12,MATCH($B$3,設定!$A$2:$A$12,0),11),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="8" t="str">
+        <v>選配</v>
+      </c>
+      <c r="C29" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D29" s="9" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,設定!$AB$2:$AJ$13,4,FALSE),""))</f>
-        <v/>
+        <v>1125×156</v>
       </c>
       <c r="E29" s="9" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,設定!$AB$2:$AJ$13,5,FALSE),""))</f>
-        <v/>
+        <v>JPG/PNG</v>
       </c>
       <c r="F29" s="10" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,設定!$AB$2:$AJ$13,6,FALSE),""))</f>
-        <v/>
+        <v>副標≤7；LOGO 1～3 個</v>
       </c>
       <c r="G29" s="10" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,設定!$AB$2:$AJ$13,7,FALSE),""))</f>
-        <v/>
+        <v>依選用版型提供 1～3 個 LOGO</v>
       </c>
       <c r="H29" s="10" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,設定!$AB$2:$AJ$13,8,FALSE),"尚未提供版型"))</f>
-        <v/>
+        <v>Search_Image1logo／2logo／3logo</v>
       </c>
       <c r="I29" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>未選</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5765,17 +5765,17 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -5955,6 +5955,21 @@
   <sheetProtection sheet="1" autoFilter="0"/>
   <autoFilter ref="A18:I30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:H11"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="A17:I17"/>
@@ -5965,21 +5980,6 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="F14:H14"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="A19:I30">
@@ -6046,7 +6046,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;L BODA 工單&amp;C 工單總覽&amp;R 第 &amp;P / &amp;N 頁</oddFooter>
   </headerFooter>
@@ -6081,148 +6081,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
       <c r="S1" s="12"/>
-      <c r="T1" s="28" t="s">
+      <c r="T1" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
     </row>
     <row r="2" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
       <c r="S2" s="13"/>
-      <c r="T2" s="29" t="s">
+      <c r="T2" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
     </row>
     <row r="3" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30" t="s">
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="T3" s="31" t="s">
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="T3" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31" t="s">
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31" t="s">
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="31"/>
-      <c r="AF3" s="31"/>
-      <c r="AG3" s="31"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
     </row>
     <row r="4" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
       <c r="C4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="33" t="s">
-        <v>452</v>
-      </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+      <c r="D4" s="45">
+        <v>300</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="6" t="str">
         <f>IF(D4="","",IF(LENB(D4)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6230,11 +6230,11 @@
       <c r="H4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="33" t="s">
-        <v>458</v>
-      </c>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
+      <c r="I4" s="35" t="s">
+        <v>457</v>
+      </c>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="6" t="str">
         <f>IF(I4="","",IF(LENB(I4)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6242,12 +6242,12 @@
       <c r="M4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="N4" s="33" t="s">
-        <v>464</v>
-      </c>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
+      <c r="N4" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
       <c r="R4" s="6" t="str">
         <f>IF(N4="","",IF(LENB(N4)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6268,16 +6268,16 @@
       <c r="AG4" s="16"/>
     </row>
     <row r="5" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>453</v>
-      </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
+      <c r="D5" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
       <c r="G5" s="6" t="str">
         <f>IF(D5="","待填","OK")</f>
         <v>OK</v>
@@ -6285,11 +6285,11 @@
       <c r="H5" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
+      <c r="I5" s="35" t="s">
+        <v>458</v>
+      </c>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="6" t="str">
         <f>IF(I5="","待填","OK")</f>
         <v>OK</v>
@@ -6297,12 +6297,12 @@
       <c r="M5" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="N5" s="23" t="s">
-        <v>465</v>
-      </c>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
+      <c r="N5" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
       <c r="R5" s="6" t="str">
         <f>IF(N5="","待填",IF(ISNUMBER(SEARCH(".",N5)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6323,16 +6323,16 @@
       <c r="AG5" s="16"/>
     </row>
     <row r="6" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>454</v>
-      </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="D6" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="6" t="str">
         <f>IF(D6="","待填",IF(ISNUMBER(SEARCH(".",D6)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6340,11 +6340,11 @@
       <c r="H6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
+      <c r="I6" s="34" t="s">
+        <v>459</v>
+      </c>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
       <c r="L6" s="6" t="str">
         <f>IF(I6="","待填",IF(ISNUMBER(SEARCH(".",I6)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6352,12 +6352,12 @@
       <c r="M6" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="N6" s="33" t="s">
-        <v>463</v>
-      </c>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
+      <c r="N6" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
       <c r="R6" s="6" t="str">
         <f>IF(N6="","",IF(LENB(N6)/2&lt;=3,"OK","超過"))</f>
         <v>OK</v>
@@ -6378,16 +6378,16 @@
       <c r="AG6" s="16"/>
     </row>
     <row r="7" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>455</v>
-      </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
+      <c r="D7" s="35" t="s">
+        <v>454</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="6" t="str">
         <f>IF(D7="","",IF(LENB(D7)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6395,11 +6395,11 @@
       <c r="H7" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="33" t="s">
-        <v>461</v>
-      </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
+      <c r="I7" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
       <c r="L7" s="6" t="str">
         <f>IF(I7="","",IF(LENB(I7)/2&lt;=4,"OK","超過"))</f>
         <v>OK</v>
@@ -6428,16 +6428,16 @@
       <c r="AG7" s="16"/>
     </row>
     <row r="8" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>456</v>
-      </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
+      <c r="D8" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="6" t="str">
         <f>IF(D8="","",IF(LENB(D8)/2&lt;=10,"OK","超過"))</f>
         <v>OK</v>
@@ -6445,11 +6445,11 @@
       <c r="H8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
+      <c r="I8" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="6" t="str">
         <f>IF(I8="","",IF(LENB(I8)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6478,16 +6478,16 @@
       <c r="AG8" s="16"/>
     </row>
     <row r="9" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
+      <c r="D9" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
       <c r="G9" s="6" t="str">
         <f>IF(D9="","",IF(LENB(D9)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6495,11 +6495,11 @@
       <c r="H9" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="33" t="s">
-        <v>463</v>
-      </c>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
+      <c r="I9" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
       <c r="L9" s="6" t="str">
         <f>IF(I9="","",IF(LENB(I9)/2&lt;=3,"OK","超過"))</f>
         <v>OK</v>
@@ -6528,30 +6528,30 @@
       <c r="AG9" s="16"/>
     </row>
     <row r="11" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
       <c r="T11" s="14" t="s">
         <v>61</v>
       </c>
@@ -6570,19 +6570,19 @@
       <c r="AG11" s="12"/>
     </row>
     <row r="12" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>466</v>
-      </c>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
+      <c r="D12" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
       <c r="J12" s="6" t="str">
         <f>IF(D12="","",IF(LENB(D12)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -6590,14 +6590,14 @@
       <c r="K12" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
+      <c r="L12" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
       <c r="R12" s="6" t="str">
         <f>IF(L12="","待填",IF(ISNUMBER(SEARCH(".",L12)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6618,19 +6618,19 @@
       <c r="AG12" s="16"/>
     </row>
     <row r="13" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
       <c r="C13" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>467</v>
-      </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
+      <c r="D13" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="6" t="str">
         <f>IF(D13="","",IF(LENB(D13)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6638,14 +6638,14 @@
       <c r="K13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="33" t="s">
-        <v>471</v>
-      </c>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
+      <c r="L13" s="35" t="s">
+        <v>470</v>
+      </c>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
       <c r="R13" s="6" t="str">
         <f>IF(L13="","待填","OK")</f>
         <v>OK</v>
@@ -6666,19 +6666,19 @@
       <c r="AG13" s="16"/>
     </row>
     <row r="14" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="33" t="s">
-        <v>468</v>
-      </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
+      <c r="D14" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
       <c r="J14" s="6" t="str">
         <f>IF(D14="","",IF(LENB(D14)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6686,14 +6686,14 @@
       <c r="K14" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="L14" s="33" t="s">
-        <v>472</v>
-      </c>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
+      <c r="L14" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
       <c r="R14" s="6" t="str">
         <f>IF(L14="","",IF(LENB(L14)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6714,19 +6714,19 @@
       <c r="AG14" s="16"/>
     </row>
     <row r="15" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>469</v>
-      </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
+      <c r="D15" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
       <c r="J15" s="6" t="str">
         <f>IF(D15="","",IF(LENB(D15)/2&lt;=9,"OK","超過"))</f>
         <v>OK</v>
@@ -6734,14 +6734,14 @@
       <c r="K15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="L15" s="33" t="s">
-        <v>473</v>
-      </c>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
+      <c r="L15" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
       <c r="R15" s="6" t="str">
         <f>IF(L15="","",IF(LENB(L15)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6762,8 +6762,8 @@
       <c r="AG15" s="16"/>
     </row>
     <row r="16" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
@@ -6775,14 +6775,14 @@
       <c r="K16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="L16" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
+      <c r="L16" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
       <c r="R16" s="6" t="str">
         <f>IF(L16="","",IF(LENB(L16)/2&lt;=5,"OK","超過"))</f>
         <v/>
@@ -6803,8 +6803,8 @@
       <c r="AG16" s="16"/>
     </row>
     <row r="17" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
@@ -6816,14 +6816,14 @@
       <c r="K17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="L17" s="33" t="s">
-        <v>474</v>
-      </c>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
+      <c r="L17" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
       <c r="R17" s="6" t="str">
         <f>IF(L17="","待填","OK")</f>
         <v>OK</v>
@@ -6844,8 +6844,8 @@
       <c r="AG17" s="16"/>
     </row>
     <row r="18" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
@@ -6857,14 +6857,14 @@
       <c r="K18" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="L18" s="33" t="s">
+      <c r="L18" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
       <c r="R18" s="6" t="str">
         <f>IF(L18="","待填","OK")</f>
         <v>OK</v>
@@ -6885,30 +6885,30 @@
       <c r="AG18" s="16"/>
     </row>
     <row r="20" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
       <c r="T20" s="14" t="s">
         <v>65</v>
       </c>
@@ -6927,27 +6927,27 @@
       <c r="AG20" s="12"/>
     </row>
     <row r="21" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
       <c r="C21" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="33" t="s">
-        <v>466</v>
-      </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
+      <c r="D21" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
       <c r="R21" s="6" t="str">
         <f>IF(D21="","",IF(LENB(D21)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -6968,27 +6968,27 @@
       <c r="AG21" s="16"/>
     </row>
     <row r="22" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="33" t="s">
-        <v>469</v>
-      </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
+      <c r="D22" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
       <c r="R22" s="6" t="str">
         <f>IF(D22="","",IF(LENB(D22)/2&lt;=10,"OK","超過"))</f>
         <v>OK</v>
@@ -7009,30 +7009,30 @@
       <c r="AG22" s="16"/>
     </row>
     <row r="23" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
       <c r="C23" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34" t="s">
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="36"/>
       <c r="T23" s="16"/>
       <c r="U23" s="16"/>
       <c r="V23" s="16"/>
@@ -7049,19 +7049,19 @@
       <c r="AG23" s="16"/>
     </row>
     <row r="24" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
       <c r="C24" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="33" t="s">
-        <v>466</v>
-      </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
+      <c r="D24" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
       <c r="J24" s="6" t="str">
         <f>IF(D24="","",IF(LENB(D24)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7069,14 +7069,14 @@
       <c r="K24" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="L24" s="33" t="s">
-        <v>466</v>
-      </c>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
+      <c r="L24" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
       <c r="R24" s="6" t="str">
         <f>IF(L24="","",IF(LENB(L24)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7097,19 +7097,19 @@
       <c r="AG24" s="16"/>
     </row>
     <row r="25" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="33"/>
       <c r="C25" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="33" t="s">
-        <v>475</v>
-      </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
+      <c r="D25" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
       <c r="J25" s="6" t="str">
         <f>IF(D25="","",IF(LENB(D25)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7117,14 +7117,14 @@
       <c r="K25" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="L25" s="33" t="s">
-        <v>475</v>
-      </c>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
+      <c r="L25" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
       <c r="R25" s="6" t="str">
         <f>IF(L25="","",IF(LENB(L25)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7145,8 +7145,8 @@
       <c r="AG25" s="16"/>
     </row>
     <row r="26" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="33"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
@@ -7179,8 +7179,8 @@
       <c r="AG26" s="16"/>
     </row>
     <row r="27" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -7213,8 +7213,8 @@
       <c r="AG27" s="16"/>
     </row>
     <row r="28" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="32"/>
-      <c r="B28" s="32"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="33"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
@@ -7247,8 +7247,8 @@
       <c r="AG28" s="16"/>
     </row>
     <row r="29" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -7281,36 +7281,36 @@
       <c r="AG29" s="16"/>
     </row>
     <row r="31" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30" t="s">
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30" t="s">
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30" t="s">
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
       <c r="T31" s="14" t="s">
         <v>69</v>
       </c>
@@ -7329,15 +7329,15 @@
       <c r="AG31" s="12"/>
     </row>
     <row r="32" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="33" t="s">
-        <v>466</v>
-      </c>
-      <c r="E32" s="33"/>
+      <c r="D32" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="E32" s="35"/>
       <c r="F32" s="6" t="str">
         <f>IF(D32="","",IF(LENB(D32)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7345,10 +7345,10 @@
       <c r="G32" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H32" s="33" t="s">
-        <v>466</v>
-      </c>
-      <c r="I32" s="33"/>
+      <c r="H32" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="I32" s="35"/>
       <c r="J32" s="6" t="str">
         <f>IF(H32="","",IF(LENB(H32)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7381,15 +7381,15 @@
       <c r="AG32" s="16"/>
     </row>
     <row r="33" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="E33" s="23"/>
+      <c r="D33" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="E33" s="34"/>
       <c r="F33" s="6" t="str">
         <f>IF(D33="","待填",IF(ISNUMBER(SEARCH(".",D33)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7397,10 +7397,10 @@
       <c r="G33" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="H33" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="I33" s="23"/>
+      <c r="H33" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="I33" s="34"/>
       <c r="J33" s="6" t="str">
         <f>IF(H33="","待填",IF(ISNUMBER(SEARCH(".",H33)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7433,15 +7433,15 @@
       <c r="AG33" s="16"/>
     </row>
     <row r="34" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="33" t="s">
-        <v>467</v>
-      </c>
-      <c r="E34" s="33"/>
+      <c r="D34" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="E34" s="35"/>
       <c r="F34" s="6" t="str">
         <f>IF(D34="","",IF(LENB(D34)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7449,10 +7449,10 @@
       <c r="G34" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H34" s="33" t="s">
-        <v>467</v>
-      </c>
-      <c r="I34" s="33"/>
+      <c r="H34" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="I34" s="35"/>
       <c r="J34" s="6" t="str">
         <f>IF(H34="","",IF(LENB(H34)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7485,15 +7485,15 @@
       <c r="AG34" s="16"/>
     </row>
     <row r="35" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="32"/>
-      <c r="B35" s="32"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="33" t="s">
-        <v>476</v>
-      </c>
-      <c r="E35" s="33"/>
+      <c r="D35" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="E35" s="35"/>
       <c r="F35" s="6" t="str">
         <f>IF(D35="","",IF(LENB(D35)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7501,10 +7501,10 @@
       <c r="G35" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H35" s="33" t="s">
-        <v>476</v>
-      </c>
-      <c r="I35" s="33"/>
+      <c r="H35" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="I35" s="35"/>
       <c r="J35" s="6" t="str">
         <f>IF(H35="","",IF(LENB(H35)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7537,15 +7537,15 @@
       <c r="AG35" s="16"/>
     </row>
     <row r="36" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="E36" s="33"/>
+      <c r="D36" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="E36" s="35"/>
       <c r="F36" s="6" t="str">
         <f>IF(D36="","",IF(LENB(D36)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -7553,10 +7553,10 @@
       <c r="G36" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="H36" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="I36" s="33"/>
+      <c r="H36" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="I36" s="35"/>
       <c r="J36" s="6" t="str">
         <f>IF(H36="","",IF(LENB(H36)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -7589,8 +7589,8 @@
       <c r="AG36" s="16"/>
     </row>
     <row r="37" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
       <c r="C37" s="17" t="s">
         <v>6</v>
       </c>
@@ -7631,36 +7631,36 @@
       <c r="AG37" s="16"/>
     </row>
     <row r="39" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30" t="s">
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30" t="s">
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30" t="s">
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
       <c r="T39" s="14" t="s">
         <v>73</v>
       </c>
@@ -7679,15 +7679,15 @@
       <c r="AG39" s="12"/>
     </row>
     <row r="40" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="32"/>
-      <c r="B40" s="32"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="33"/>
       <c r="C40" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="E40" s="23"/>
+      <c r="D40" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="E40" s="34"/>
       <c r="F40" s="6" t="str">
         <f>IF(D40="","待填",IF(ISNUMBER(SEARCH(".",D40)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7695,10 +7695,10 @@
       <c r="G40" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H40" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="I40" s="23"/>
+      <c r="H40" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="I40" s="34"/>
       <c r="J40" s="6" t="str">
         <f>IF(H40="","待填",IF(ISNUMBER(SEARCH(".",H40)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7706,10 +7706,10 @@
       <c r="K40" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="L40" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="M40" s="23"/>
+      <c r="L40" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="M40" s="34"/>
       <c r="N40" s="6" t="str">
         <f>IF(L40="","待填",IF(ISNUMBER(SEARCH(".",L40)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7736,15 +7736,15 @@
       <c r="AG40" s="16"/>
     </row>
     <row r="41" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="32"/>
-      <c r="B41" s="32"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="33" t="s">
-        <v>477</v>
-      </c>
-      <c r="E41" s="33"/>
+      <c r="D41" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E41" s="35"/>
       <c r="F41" s="6" t="str">
         <f>IF(D41="","",IF(LENB(D41)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -7752,10 +7752,10 @@
       <c r="G41" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H41" s="33" t="s">
-        <v>477</v>
-      </c>
-      <c r="I41" s="33"/>
+      <c r="H41" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="I41" s="35"/>
       <c r="J41" s="6" t="str">
         <f>IF(H41="","",IF(LENB(H41)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -7763,10 +7763,10 @@
       <c r="K41" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="L41" s="33" t="s">
-        <v>477</v>
-      </c>
-      <c r="M41" s="33"/>
+      <c r="L41" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="M41" s="35"/>
       <c r="N41" s="6" t="str">
         <f>IF(L41="","",IF(LENB(L41)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -7793,15 +7793,15 @@
       <c r="AG41" s="16"/>
     </row>
     <row r="42" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="32"/>
-      <c r="B42" s="32"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="33"/>
       <c r="C42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="E42" s="33"/>
+      <c r="D42" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="E42" s="35"/>
       <c r="F42" s="6" t="str">
         <f>IF(D42="","",IF(LENB(D42)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7809,10 +7809,10 @@
       <c r="G42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="H42" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="I42" s="33"/>
+      <c r="H42" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="I42" s="35"/>
       <c r="J42" s="6" t="str">
         <f>IF(H42="","",IF(LENB(H42)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7820,10 +7820,10 @@
       <c r="K42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="L42" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="M42" s="33"/>
+      <c r="L42" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="M42" s="35"/>
       <c r="N42" s="6" t="str">
         <f>IF(L42="","",IF(LENB(L42)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7850,8 +7850,8 @@
       <c r="AG42" s="16"/>
     </row>
     <row r="43" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="32"/>
-      <c r="B43" s="32"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="33"/>
       <c r="C43" s="17" t="s">
         <v>6</v>
       </c>
@@ -7892,8 +7892,8 @@
       <c r="AG43" s="16"/>
     </row>
     <row r="44" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="32"/>
-      <c r="B44" s="32"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="33"/>
       <c r="C44" s="17" t="s">
         <v>6</v>
       </c>
@@ -7934,8 +7934,8 @@
       <c r="AG44" s="16"/>
     </row>
     <row r="45" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="32"/>
-      <c r="B45" s="32"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="33"/>
       <c r="C45" s="17" t="s">
         <v>6</v>
       </c>
@@ -7978,227 +7978,227 @@
     <row r="47" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
-      <c r="C47" s="35" t="s">
+      <c r="C47" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35" t="s">
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="35"/>
-      <c r="M47" s="35" t="s">
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35" t="s">
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-      <c r="U47" s="35"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="35"/>
-      <c r="X47" s="35"/>
-      <c r="Y47" s="35"/>
-      <c r="Z47" s="35" t="s">
+      <c r="S47" s="31"/>
+      <c r="T47" s="31"/>
+      <c r="U47" s="31"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="31"/>
+      <c r="X47" s="31"/>
+      <c r="Y47" s="31"/>
+      <c r="Z47" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="AA47" s="35"/>
-      <c r="AB47" s="35"/>
-      <c r="AC47" s="35"/>
-      <c r="AD47" s="35"/>
-      <c r="AE47" s="35"/>
-      <c r="AF47" s="35"/>
-      <c r="AG47" s="35"/>
+      <c r="AA47" s="31"/>
+      <c r="AB47" s="31"/>
+      <c r="AC47" s="31"/>
+      <c r="AD47" s="31"/>
+      <c r="AE47" s="31"/>
+      <c r="AF47" s="31"/>
+      <c r="AG47" s="31"/>
     </row>
     <row r="48" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="40" t="s">
+      <c r="C48" s="23" t="s">
         <v>114</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E48" s="36" t="s">
-        <v>481</v>
-      </c>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="40" t="s">
+      <c r="E48" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="23" t="s">
         <v>114</v>
       </c>
       <c r="I48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="J48" s="36" t="s">
+      <c r="J48" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="K48" s="36"/>
-      <c r="L48" s="36"/>
-      <c r="M48" s="40" t="s">
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="23" t="s">
         <v>114</v>
       </c>
       <c r="N48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="O48" s="37" t="s">
+      <c r="O48" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="P48" s="37"/>
-      <c r="Q48" s="37"/>
-      <c r="R48" s="40" t="s">
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22"/>
+      <c r="R48" s="23" t="s">
         <v>114</v>
       </c>
       <c r="S48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="T48" s="37" t="s">
+      <c r="T48" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="U48" s="37"/>
-      <c r="V48" s="37"/>
-      <c r="W48" s="37"/>
-      <c r="X48" s="37"/>
-      <c r="Y48" s="37"/>
-      <c r="Z48" s="40" t="s">
+      <c r="U48" s="22"/>
+      <c r="V48" s="22"/>
+      <c r="W48" s="22"/>
+      <c r="X48" s="22"/>
+      <c r="Y48" s="22"/>
+      <c r="Z48" s="23" t="s">
         <v>114</v>
       </c>
       <c r="AA48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="AB48" s="37" t="s">
+      <c r="AB48" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="AC48" s="37"/>
-      <c r="AD48" s="37"/>
-      <c r="AE48" s="37"/>
-      <c r="AF48" s="37"/>
-      <c r="AG48" s="37"/>
+      <c r="AC48" s="22"/>
+      <c r="AD48" s="22"/>
+      <c r="AE48" s="22"/>
+      <c r="AF48" s="22"/>
+      <c r="AG48" s="22"/>
     </row>
     <row r="49" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="38"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="40"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="23"/>
       <c r="D49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E49" s="36" t="s">
+      <c r="E49" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="40"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="23"/>
       <c r="I49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="J49" s="36" t="s">
-        <v>480</v>
-      </c>
-      <c r="K49" s="36"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="40"/>
+      <c r="J49" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="23"/>
       <c r="N49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="O49" s="37" t="s">
-        <v>480</v>
-      </c>
-      <c r="P49" s="37"/>
-      <c r="Q49" s="37"/>
-      <c r="R49" s="40"/>
+      <c r="O49" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22"/>
+      <c r="R49" s="23"/>
       <c r="S49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="T49" s="37" t="s">
-        <v>484</v>
-      </c>
-      <c r="U49" s="37"/>
-      <c r="V49" s="37"/>
-      <c r="W49" s="37"/>
-      <c r="X49" s="37"/>
-      <c r="Y49" s="37"/>
-      <c r="Z49" s="40"/>
+      <c r="T49" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="U49" s="22"/>
+      <c r="V49" s="22"/>
+      <c r="W49" s="22"/>
+      <c r="X49" s="22"/>
+      <c r="Y49" s="22"/>
+      <c r="Z49" s="23"/>
       <c r="AA49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="AB49" s="37" t="s">
+      <c r="AB49" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="AC49" s="37"/>
-      <c r="AD49" s="37"/>
-      <c r="AE49" s="37"/>
-      <c r="AF49" s="37"/>
-      <c r="AG49" s="37"/>
+      <c r="AC49" s="22"/>
+      <c r="AD49" s="22"/>
+      <c r="AE49" s="22"/>
+      <c r="AF49" s="22"/>
+      <c r="AG49" s="22"/>
     </row>
     <row r="50" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="38"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="43" t="s">
-        <v>479</v>
-      </c>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
       <c r="G50" s="21">
         <f>IF(OR(C50="",C50="文案5字內"),"",LENB(C50)/2)</f>
         <v>3</v>
       </c>
-      <c r="H50" s="44" t="s">
-        <v>483</v>
-      </c>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
+      <c r="H50" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
       <c r="L50" s="21">
         <f>IF(OR(H50="",H50="文案5字內"),"",LENB(H50)/2)</f>
         <v>2.5</v>
       </c>
-      <c r="M50" s="42" t="s">
-        <v>483</v>
-      </c>
-      <c r="N50" s="42"/>
-      <c r="O50" s="42"/>
-      <c r="P50" s="42"/>
+      <c r="M50" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="N50" s="27"/>
+      <c r="O50" s="27"/>
+      <c r="P50" s="27"/>
       <c r="Q50" s="21">
         <f>IF(OR(M50="",M50="(需要再填即可)"),"",LENB(M50)/2)</f>
         <v>2.5</v>
       </c>
-      <c r="R50" s="42" t="s">
-        <v>482</v>
-      </c>
-      <c r="S50" s="42"/>
-      <c r="T50" s="42"/>
-      <c r="U50" s="42"/>
-      <c r="V50" s="42"/>
-      <c r="W50" s="42"/>
-      <c r="X50" s="42"/>
+      <c r="R50" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="S50" s="27"/>
+      <c r="T50" s="27"/>
+      <c r="U50" s="27"/>
+      <c r="V50" s="27"/>
+      <c r="W50" s="27"/>
+      <c r="X50" s="27"/>
       <c r="Y50" s="21">
         <f>IF(OR(R50="",R50="(需要再填即可)"),"",LENB(R50)/2)</f>
         <v>2.5</v>
       </c>
-      <c r="Z50" s="42" t="s">
+      <c r="Z50" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="AA50" s="42"/>
-      <c r="AB50" s="42"/>
-      <c r="AC50" s="42"/>
-      <c r="AD50" s="42"/>
-      <c r="AE50" s="42"/>
-      <c r="AF50" s="42"/>
+      <c r="AA50" s="27"/>
+      <c r="AB50" s="27"/>
+      <c r="AC50" s="27"/>
+      <c r="AD50" s="27"/>
+      <c r="AE50" s="27"/>
+      <c r="AF50" s="27"/>
       <c r="AG50" s="21" t="str">
         <f>IF(OR(Z50="",Z50="(需要再填即可)"),"",LENB(Z50)/2)</f>
         <v/>
@@ -8208,94 +8208,6 @@
   <sheetProtection sheet="1" autoFilter="0"/>
   <autoFilter ref="A1:AG1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="112">
-    <mergeCell ref="T49:Y49"/>
-    <mergeCell ref="Z48:Z49"/>
-    <mergeCell ref="AB49:AG49"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="M50:P50"/>
-    <mergeCell ref="R50:X50"/>
-    <mergeCell ref="Z50:AF50"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="M48:M49"/>
-    <mergeCell ref="O49:Q49"/>
-    <mergeCell ref="R48:R49"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:L47"/>
-    <mergeCell ref="M47:Q47"/>
-    <mergeCell ref="R47:Y47"/>
-    <mergeCell ref="Z47:AG47"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="O48:Q48"/>
-    <mergeCell ref="T48:Y48"/>
-    <mergeCell ref="AB48:AG48"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="B39:B45"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="A31:A37"/>
-    <mergeCell ref="B31:B37"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="C20:R20"/>
-    <mergeCell ref="A20:A29"/>
-    <mergeCell ref="B20:B29"/>
-    <mergeCell ref="D21:Q21"/>
-    <mergeCell ref="D22:Q22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="K23:R23"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="L24:Q24"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="L25:Q25"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C11:R11"/>
-    <mergeCell ref="A11:A18"/>
-    <mergeCell ref="B11:B18"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="L16:Q16"/>
-    <mergeCell ref="L17:Q17"/>
-    <mergeCell ref="L18:Q18"/>
     <mergeCell ref="C1:R1"/>
     <mergeCell ref="T1:AG1"/>
     <mergeCell ref="A1:A2"/>
@@ -8320,6 +8232,94 @@
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="N6:Q6"/>
     <mergeCell ref="D7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="C11:R11"/>
+    <mergeCell ref="A11:A18"/>
+    <mergeCell ref="B11:B18"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="L15:Q15"/>
+    <mergeCell ref="L16:Q16"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="C20:R20"/>
+    <mergeCell ref="A20:A29"/>
+    <mergeCell ref="B20:B29"/>
+    <mergeCell ref="D21:Q21"/>
+    <mergeCell ref="D22:Q22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="K23:R23"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="L24:Q24"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="L25:Q25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="A31:A37"/>
+    <mergeCell ref="B31:B37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="B39:B45"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:L47"/>
+    <mergeCell ref="M47:Q47"/>
+    <mergeCell ref="R47:Y47"/>
+    <mergeCell ref="Z47:AG47"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="O48:Q48"/>
+    <mergeCell ref="T48:Y48"/>
+    <mergeCell ref="AB48:AG48"/>
+    <mergeCell ref="T49:Y49"/>
+    <mergeCell ref="Z48:Z49"/>
+    <mergeCell ref="AB49:AG49"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="M50:P50"/>
+    <mergeCell ref="R50:X50"/>
+    <mergeCell ref="Z50:AF50"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="O49:Q49"/>
+    <mergeCell ref="R48:R49"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="C50">
@@ -8408,31 +8408,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F36">
-    <cfRule type="expression" dxfId="84" priority="155">
-      <formula>F32="記得加副檔名"</formula>
+    <cfRule type="expression" dxfId="84" priority="153">
+      <formula>F32="超過"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="83" priority="156">
       <formula>F32="OK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="154">
+    <cfRule type="expression" dxfId="82" priority="155">
+      <formula>F32="記得加副檔名"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="154">
       <formula>F32="禁用語"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="153">
-      <formula>F32="超過"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F40:F42">
     <cfRule type="expression" dxfId="80" priority="200">
       <formula>F40="超過"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="201">
-      <formula>F40="禁用語"</formula>
+    <cfRule type="expression" dxfId="79" priority="203">
+      <formula>F40="OK"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="78" priority="202">
       <formula>F40="記得加副檔名"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="203">
-      <formula>F40="OK"</formula>
+    <cfRule type="expression" dxfId="77" priority="201">
+      <formula>F40="禁用語"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G9">
@@ -8508,59 +8508,59 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12:J15">
-    <cfRule type="expression" dxfId="60" priority="75">
+    <cfRule type="expression" dxfId="60" priority="74">
+      <formula>J12="記得加副檔名"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="75">
       <formula>J12="OK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="72">
-      <formula>J12="超過"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="58" priority="73">
       <formula>J12="禁用語"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="74">
-      <formula>J12="記得加副檔名"</formula>
+    <cfRule type="expression" dxfId="57" priority="72">
+      <formula>J12="超過"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J24:J25">
-    <cfRule type="expression" dxfId="56" priority="135">
+    <cfRule type="expression" dxfId="56" priority="133">
+      <formula>J24="超過"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="136">
+      <formula>J24="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="135">
       <formula>J24="記得加副檔名"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="134">
+    <cfRule type="expression" dxfId="53" priority="134">
       <formula>J24="禁用語"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="133">
-      <formula>J24="超過"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="136">
-      <formula>J24="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32:J36">
-    <cfRule type="expression" dxfId="52" priority="180">
-      <formula>J32="OK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="178">
+    <cfRule type="expression" dxfId="52" priority="178">
       <formula>J32="禁用語"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="177">
+    <cfRule type="expression" dxfId="51" priority="177">
       <formula>J32="超過"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="179">
+    <cfRule type="expression" dxfId="50" priority="179">
       <formula>J32="記得加副檔名"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="180">
+      <formula>J32="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J40:J42">
     <cfRule type="expression" dxfId="48" priority="216">
       <formula>J40="記得加副檔名"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="215">
-      <formula>J40="禁用語"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="217">
+    <cfRule type="expression" dxfId="47" priority="217">
       <formula>J40="OK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="214">
+    <cfRule type="expression" dxfId="46" priority="214">
       <formula>J40="超過"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="215">
+      <formula>J40="禁用語"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J48:J49">
@@ -8569,17 +8569,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L9">
-    <cfRule type="expression" dxfId="43" priority="33">
-      <formula>L4="OK"</formula>
+    <cfRule type="expression" dxfId="43" priority="31">
+      <formula>L4="禁用語"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="42" priority="32">
       <formula>L4="記得加副檔名"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="31">
-      <formula>L4="禁用語"</formula>
+    <cfRule type="expression" dxfId="41" priority="30">
+      <formula>L4="超過"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="30">
-      <formula>L4="超過"</formula>
+    <cfRule type="expression" dxfId="40" priority="33">
+      <formula>L4="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14:L16">
@@ -8626,17 +8626,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N40:N42">
-    <cfRule type="expression" dxfId="30" priority="231">
-      <formula>N40="OK"</formula>
+    <cfRule type="expression" dxfId="30" priority="229">
+      <formula>N40="禁用語"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="230">
+    <cfRule type="expression" dxfId="29" priority="228">
+      <formula>N40="超過"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="230">
       <formula>N40="記得加副檔名"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="228">
-      <formula>N40="超過"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="229">
-      <formula>N40="禁用語"</formula>
+    <cfRule type="expression" dxfId="27" priority="231">
+      <formula>N40="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O48:O49">
@@ -8645,11 +8645,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q50">
-    <cfRule type="expression" dxfId="25" priority="253">
+    <cfRule type="expression" dxfId="25" priority="252">
+      <formula>Q50&gt;5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="253">
       <formula>AND(ISNUMBER(Q50),Q50&lt;=5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="252">
-      <formula>Q50&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:R6">
@@ -8670,42 +8670,42 @@
     <cfRule type="expression" dxfId="19" priority="77">
       <formula>R12="禁用語"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="78">
-      <formula>R12="記得加副檔名"</formula>
+    <cfRule type="expression" dxfId="18" priority="76">
+      <formula>R12="超過"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="79">
       <formula>R12="OK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="76">
-      <formula>R12="超過"</formula>
+    <cfRule type="expression" dxfId="16" priority="78">
+      <formula>R12="記得加副檔名"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R21:R22">
-    <cfRule type="expression" dxfId="15" priority="126">
+    <cfRule type="expression" dxfId="15" priority="124">
+      <formula>R21="禁用語"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="126">
       <formula>R21="OK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="125">
+    <cfRule type="expression" dxfId="13" priority="123">
+      <formula>R21="超過"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="125">
       <formula>R21="記得加副檔名"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="124">
-      <formula>R21="禁用語"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="123">
-      <formula>R21="超過"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R24:R25">
-    <cfRule type="expression" dxfId="11" priority="138">
+    <cfRule type="expression" dxfId="11" priority="141">
+      <formula>R24="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="138">
       <formula>R24="超過"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="139">
+    <cfRule type="expression" dxfId="9" priority="139">
       <formula>R24="禁用語"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="140">
+    <cfRule type="expression" dxfId="8" priority="140">
       <formula>R24="記得加副檔名"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="141">
-      <formula>R24="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R50">
@@ -8719,11 +8719,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y50">
-    <cfRule type="expression" dxfId="5" priority="257">
+    <cfRule type="expression" dxfId="5" priority="256">
+      <formula>Y50&gt;5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="257">
       <formula>AND(ISNUMBER(Y50),Y50&lt;=5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="256">
-      <formula>Y50&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z50">
@@ -8737,11 +8737,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG50">
-    <cfRule type="expression" dxfId="1" priority="261">
+    <cfRule type="expression" dxfId="1" priority="260">
+      <formula>AG50&gt;5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="261">
       <formula>AND(ISNUMBER(AG50),AG50&lt;=5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="260">
-      <formula>AG50&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="12">

--- a/測試工單與圖片/BODA工單_brand_star_mega_zj_1787896948520.xlsx
+++ b/測試工單與圖片/BODA工單_brand_star_mega_zj_1787896948520.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF77DEF-318E-43CB-8FD3-4A42D5BB195A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EC29B1-85E9-493D-B401-10538C6EA7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -444,7 +444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L24" authorId="0" shapeId="0" xr:uid="{4974B5C8-6342-4022-BBC5-EEF7397EBDCF}">
+    <comment ref="L24" authorId="0" shapeId="0" xr:uid="{9A435EE9-C843-4524-88F1-CBED430D3254}">
       <text>
         <r>
           <rPr>
@@ -497,6 +497,21 @@
             <scheme val="minor"/>
           </rPr>
           <t>填寫規則：促標6個字內</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F32" authorId="0" shapeId="0" xr:uid="{C65A64B6-6CDA-4A06-B0CF-4FE8C4DE5FEA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">作者:
+</t>
         </r>
       </text>
     </comment>
@@ -556,7 +571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{047186B3-52AD-4FE0-808D-A9F9518BB27B}">
+    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{7BEA452D-9D33-45C2-901C-CF2E1C191A22}">
       <text>
         <r>
           <rPr>
@@ -682,7 +697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H41" authorId="0" shapeId="0" xr:uid="{1322B85B-A236-4F71-8A5B-D8C13E1F6394}">
+    <comment ref="H41" authorId="0" shapeId="0" xr:uid="{EE946598-77DB-479A-A614-242F715B12A3}">
       <text>
         <r>
           <rPr>
@@ -696,7 +711,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L41" authorId="0" shapeId="0" xr:uid="{8215F455-4880-4087-94CE-5D26AA346655}">
+    <comment ref="L41" authorId="0" shapeId="0" xr:uid="{A21C86EF-DCB0-420C-83ED-D18075462641}">
       <text>
         <r>
           <rPr>
@@ -1037,7 +1052,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="487">
   <si>
     <t>BODA 工單總覽</t>
   </si>
@@ -2618,22 +2633,6 @@
   </si>
   <si>
     <r>
-      <t>100W</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>變壓器</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Plainme_YOBI </t>
     </r>
     <r>
@@ -2702,6 +2701,62 @@
   <si>
     <t>Dyson_Logo480x360去背版.png</t>
   </si>
+  <si>
+    <t>滿200送20</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>滿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>送</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>100W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>變壓器</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>超值變壓器</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2712,7 +2767,7 @@
     <numFmt numFmtId="177" formatCode="\$#,##0"/>
     <numFmt numFmtId="178" formatCode="0.0;\-0.0;0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2870,6 +2925,20 @@
       <color rgb="FF0000FF"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -3053,7 +3122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3112,6 +3181,43 @@
     <xf numFmtId="178" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3141,41 +3247,11 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3184,13 +3260,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="27" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -5007,35 +5084,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="44">
+      <c r="F3" s="42">
         <f>IFERROR(VLOOKUP(B3,設定!$A$2:$B$12,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="44"/>
+      <c r="G3" s="42"/>
       <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
@@ -5047,18 +5124,18 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
+      <c r="B4" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="34"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
@@ -5070,18 +5147,18 @@
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="34"/>
+      <c r="F5" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="29"/>
       <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
@@ -5094,85 +5171,85 @@
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
       <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
+      <c r="F6" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
+      <c r="B7" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
+      <c r="B11" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
       <c r="I11" s="6" t="str">
         <f>IF(B11="","",IF(LENB(B11)/2&lt;=9,"OK","超過"))</f>
         <v/>
@@ -5182,19 +5259,19 @@
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
+      <c r="B12" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
       <c r="E12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
       <c r="I12" s="6" t="str">
         <f>IF(B12="","",IF(LENB(B12)/2&lt;=8,"OK","超過"))</f>
         <v/>
@@ -5204,19 +5281,19 @@
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
+      <c r="B13" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="6" t="str">
         <f>IF(B13="","",IF(LENB(B13)/2&lt;=7,"OK","超過"))</f>
         <v/>
@@ -5226,19 +5303,19 @@
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
+      <c r="B14" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="6" t="str">
         <f>IF(B14="","",IF(LENB(B14)/2&lt;=14,"OK","超過"))</f>
         <v/>
@@ -5248,36 +5325,36 @@
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
+      <c r="B15" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
       <c r="I15" s="6" t="str">
         <f>IF(B15="","",IF(LENB(B15)/2&lt;=2,"OK","超過"))</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -5765,17 +5842,17 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -5955,21 +6032,6 @@
   <sheetProtection sheet="1" autoFilter="0"/>
   <autoFilter ref="A18:I30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:H11"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="A17:I17"/>
@@ -5980,6 +6042,21 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="F14:H14"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="A19:I30">
@@ -6081,148 +6158,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
       <c r="S1" s="12"/>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
     </row>
     <row r="2" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38" t="s">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
       <c r="S2" s="13"/>
-      <c r="T2" s="38" t="s">
+      <c r="T2" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
     </row>
     <row r="3" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32" t="s">
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32" t="s">
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="T3" s="39" t="s">
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="T3" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39" t="s">
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39" t="s">
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
     </row>
     <row r="4" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="27">
         <v>300</v>
       </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="6" t="str">
         <f>IF(D4="","",IF(LENB(D4)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6230,11 +6307,11 @@
       <c r="H4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="28" t="s">
         <v>457</v>
       </c>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
       <c r="L4" s="6" t="str">
         <f>IF(I4="","",IF(LENB(I4)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6242,12 +6319,12 @@
       <c r="M4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="N4" s="35" t="s">
+      <c r="N4" s="28" t="s">
         <v>463</v>
       </c>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
       <c r="R4" s="6" t="str">
         <f>IF(N4="","",IF(LENB(N4)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6268,16 +6345,16 @@
       <c r="AG4" s="16"/>
     </row>
     <row r="5" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="28" t="s">
         <v>452</v>
       </c>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
       <c r="G5" s="6" t="str">
         <f>IF(D5="","待填","OK")</f>
         <v>OK</v>
@@ -6285,11 +6362,11 @@
       <c r="H5" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="28" t="s">
         <v>458</v>
       </c>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
       <c r="L5" s="6" t="str">
         <f>IF(I5="","待填","OK")</f>
         <v>OK</v>
@@ -6297,12 +6374,12 @@
       <c r="M5" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="29" t="s">
         <v>464</v>
       </c>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
       <c r="R5" s="6" t="str">
         <f>IF(N5="","待填",IF(ISNUMBER(SEARCH(".",N5)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6323,16 +6400,16 @@
       <c r="AG5" s="16"/>
     </row>
     <row r="6" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="29" t="s">
         <v>453</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="6" t="str">
         <f>IF(D6="","待填",IF(ISNUMBER(SEARCH(".",D6)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6340,11 +6417,11 @@
       <c r="H6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="29" t="s">
         <v>459</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
       <c r="L6" s="6" t="str">
         <f>IF(I6="","待填",IF(ISNUMBER(SEARCH(".",I6)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6352,12 +6429,12 @@
       <c r="M6" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="N6" s="35" t="s">
+      <c r="N6" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
       <c r="R6" s="6" t="str">
         <f>IF(N6="","",IF(LENB(N6)/2&lt;=3,"OK","超過"))</f>
         <v>OK</v>
@@ -6378,16 +6455,16 @@
       <c r="AG6" s="16"/>
     </row>
     <row r="7" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="28" t="s">
         <v>454</v>
       </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
       <c r="G7" s="6" t="str">
         <f>IF(D7="","",IF(LENB(D7)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6395,11 +6472,11 @@
       <c r="H7" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
       <c r="L7" s="6" t="str">
         <f>IF(I7="","",IF(LENB(I7)/2&lt;=4,"OK","超過"))</f>
         <v>OK</v>
@@ -6428,16 +6505,16 @@
       <c r="AG7" s="16"/>
     </row>
     <row r="8" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="28" t="s">
         <v>455</v>
       </c>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
       <c r="G8" s="6" t="str">
         <f>IF(D8="","",IF(LENB(D8)/2&lt;=10,"OK","超過"))</f>
         <v>OK</v>
@@ -6445,11 +6522,11 @@
       <c r="H8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
       <c r="L8" s="6" t="str">
         <f>IF(I8="","",IF(LENB(I8)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6478,16 +6555,16 @@
       <c r="AG8" s="16"/>
     </row>
     <row r="9" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
       <c r="G9" s="6" t="str">
         <f>IF(D9="","",IF(LENB(D9)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6495,11 +6572,11 @@
       <c r="H9" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
       <c r="L9" s="6" t="str">
         <f>IF(I9="","",IF(LENB(I9)/2&lt;=3,"OK","超過"))</f>
         <v>OK</v>
@@ -6528,30 +6605,30 @@
       <c r="AG9" s="16"/>
     </row>
     <row r="11" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
       <c r="T11" s="14" t="s">
         <v>61</v>
       </c>
@@ -6570,19 +6647,19 @@
       <c r="AG11" s="12"/>
     </row>
     <row r="12" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="28" t="s">
         <v>465</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
       <c r="J12" s="6" t="str">
         <f>IF(D12="","",IF(LENB(D12)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -6590,14 +6667,14 @@
       <c r="K12" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="29" t="s">
         <v>469</v>
       </c>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
       <c r="R12" s="6" t="str">
         <f>IF(L12="","待填",IF(ISNUMBER(SEARCH(".",L12)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -6618,19 +6695,19 @@
       <c r="AG12" s="16"/>
     </row>
     <row r="13" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="28" t="s">
         <v>466</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
       <c r="J13" s="6" t="str">
         <f>IF(D13="","",IF(LENB(D13)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6638,14 +6715,14 @@
       <c r="K13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="35" t="s">
+      <c r="L13" s="28" t="s">
         <v>470</v>
       </c>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
       <c r="R13" s="6" t="str">
         <f>IF(L13="","待填","OK")</f>
         <v>OK</v>
@@ -6666,19 +6743,19 @@
       <c r="AG13" s="16"/>
     </row>
     <row r="14" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="28" t="s">
         <v>467</v>
       </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
       <c r="J14" s="6" t="str">
         <f>IF(D14="","",IF(LENB(D14)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -6686,14 +6763,14 @@
       <c r="K14" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="L14" s="35" t="s">
+      <c r="L14" s="28" t="s">
         <v>471</v>
       </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
       <c r="R14" s="6" t="str">
         <f>IF(L14="","",IF(LENB(L14)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6714,19 +6791,19 @@
       <c r="AG14" s="16"/>
     </row>
     <row r="15" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="28" t="s">
         <v>468</v>
       </c>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
       <c r="J15" s="6" t="str">
         <f>IF(D15="","",IF(LENB(D15)/2&lt;=9,"OK","超過"))</f>
         <v>OK</v>
@@ -6734,14 +6811,14 @@
       <c r="K15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="L15" s="35" t="s">
+      <c r="L15" s="28" t="s">
         <v>472</v>
       </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
       <c r="R15" s="6" t="str">
         <f>IF(L15="","",IF(LENB(L15)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -6762,8 +6839,8 @@
       <c r="AG15" s="16"/>
     </row>
     <row r="16" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
@@ -6775,14 +6852,14 @@
       <c r="K16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="L16" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
+      <c r="L16" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
       <c r="R16" s="6" t="str">
         <f>IF(L16="","",IF(LENB(L16)/2&lt;=5,"OK","超過"))</f>
         <v/>
@@ -6803,8 +6880,8 @@
       <c r="AG16" s="16"/>
     </row>
     <row r="17" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
@@ -6816,14 +6893,14 @@
       <c r="K17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="L17" s="35" t="s">
+      <c r="L17" s="28" t="s">
         <v>473</v>
       </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
       <c r="R17" s="6" t="str">
         <f>IF(L17="","待填","OK")</f>
         <v>OK</v>
@@ -6844,8 +6921,8 @@
       <c r="AG17" s="16"/>
     </row>
     <row r="18" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
@@ -6857,14 +6934,14 @@
       <c r="K18" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="L18" s="35" t="s">
+      <c r="L18" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
       <c r="R18" s="6" t="str">
         <f>IF(L18="","待填","OK")</f>
         <v>OK</v>
@@ -6885,30 +6962,30 @@
       <c r="AG18" s="16"/>
     </row>
     <row r="20" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
       <c r="T20" s="14" t="s">
         <v>65</v>
       </c>
@@ -6927,27 +7004,27 @@
       <c r="AG20" s="12"/>
     </row>
     <row r="21" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="28" t="s">
         <v>465</v>
       </c>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
       <c r="R21" s="6" t="str">
         <f>IF(D21="","",IF(LENB(D21)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -6968,27 +7045,27 @@
       <c r="AG21" s="16"/>
     </row>
     <row r="22" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="28" t="s">
         <v>468</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
       <c r="R22" s="6" t="str">
         <f>IF(D22="","",IF(LENB(D22)/2&lt;=10,"OK","超過"))</f>
         <v>OK</v>
@@ -7009,30 +7086,30 @@
       <c r="AG22" s="16"/>
     </row>
     <row r="23" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36" t="s">
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="36"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
       <c r="T23" s="16"/>
       <c r="U23" s="16"/>
       <c r="V23" s="16"/>
@@ -7049,19 +7126,19 @@
       <c r="AG23" s="16"/>
     </row>
     <row r="24" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
+      <c r="D24" s="46" t="s">
+        <v>484</v>
+      </c>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
       <c r="J24" s="6" t="str">
         <f>IF(D24="","",IF(LENB(D24)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7069,14 +7146,14 @@
       <c r="K24" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="L24" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
+      <c r="L24" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
       <c r="R24" s="6" t="str">
         <f>IF(L24="","",IF(LENB(L24)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7097,19 +7174,19 @@
       <c r="AG24" s="16"/>
     </row>
     <row r="25" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="33"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="35" t="s">
+      <c r="D25" s="28" t="s">
         <v>474</v>
       </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
       <c r="J25" s="6" t="str">
         <f>IF(D25="","",IF(LENB(D25)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7117,14 +7194,14 @@
       <c r="K25" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="L25" s="35" t="s">
+      <c r="L25" s="28" t="s">
         <v>474</v>
       </c>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
       <c r="R25" s="6" t="str">
         <f>IF(L25="","",IF(LENB(L25)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7145,8 +7222,8 @@
       <c r="AG25" s="16"/>
     </row>
     <row r="26" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
-      <c r="B26" s="33"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
@@ -7179,8 +7256,8 @@
       <c r="AG26" s="16"/>
     </row>
     <row r="27" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -7213,8 +7290,8 @@
       <c r="AG27" s="16"/>
     </row>
     <row r="28" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
@@ -7247,8 +7324,8 @@
       <c r="AG28" s="16"/>
     </row>
     <row r="29" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -7281,36 +7358,36 @@
       <c r="AG29" s="16"/>
     </row>
     <row r="31" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
+      <c r="A31" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32" t="s">
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32" t="s">
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32" t="s">
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
       <c r="T31" s="14" t="s">
         <v>69</v>
       </c>
@@ -7329,15 +7406,15 @@
       <c r="AG31" s="12"/>
     </row>
     <row r="32" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="E32" s="35"/>
+      <c r="D32" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="E32" s="28"/>
       <c r="F32" s="6" t="str">
         <f>IF(D32="","",IF(LENB(D32)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7345,10 +7422,10 @@
       <c r="G32" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="28" t="s">
         <v>465</v>
       </c>
-      <c r="I32" s="35"/>
+      <c r="I32" s="28"/>
       <c r="J32" s="6" t="str">
         <f>IF(H32="","",IF(LENB(H32)/2&lt;=6,"OK","超過"))</f>
         <v>OK</v>
@@ -7381,15 +7458,15 @@
       <c r="AG32" s="16"/>
     </row>
     <row r="33" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="33"/>
-      <c r="B33" s="33"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
       <c r="C33" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="34" t="s">
+      <c r="D33" s="29" t="s">
         <v>469</v>
       </c>
-      <c r="E33" s="34"/>
+      <c r="E33" s="29"/>
       <c r="F33" s="6" t="str">
         <f>IF(D33="","待填",IF(ISNUMBER(SEARCH(".",D33)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7397,10 +7474,10 @@
       <c r="G33" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="H33" s="34" t="s">
+      <c r="H33" s="29" t="s">
         <v>469</v>
       </c>
-      <c r="I33" s="34"/>
+      <c r="I33" s="29"/>
       <c r="J33" s="6" t="str">
         <f>IF(H33="","待填",IF(ISNUMBER(SEARCH(".",H33)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7433,15 +7510,15 @@
       <c r="AG33" s="16"/>
     </row>
     <row r="34" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="E34" s="35"/>
+      <c r="D34" s="47" t="s">
+        <v>485</v>
+      </c>
+      <c r="E34" s="28"/>
       <c r="F34" s="6" t="str">
         <f>IF(D34="","",IF(LENB(D34)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7449,10 +7526,10 @@
       <c r="G34" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H34" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="I34" s="35"/>
+      <c r="H34" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="I34" s="28"/>
       <c r="J34" s="6" t="str">
         <f>IF(H34="","",IF(LENB(H34)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7485,15 +7562,15 @@
       <c r="AG34" s="16"/>
     </row>
     <row r="35" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="33"/>
-      <c r="B35" s="33"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="26"/>
       <c r="C35" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="28" t="s">
         <v>475</v>
       </c>
-      <c r="E35" s="35"/>
+      <c r="E35" s="28"/>
       <c r="F35" s="6" t="str">
         <f>IF(D35="","",IF(LENB(D35)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7501,10 +7578,10 @@
       <c r="G35" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H35" s="35" t="s">
+      <c r="H35" s="28" t="s">
         <v>475</v>
       </c>
-      <c r="I35" s="35"/>
+      <c r="I35" s="28"/>
       <c r="J35" s="6" t="str">
         <f>IF(H35="","",IF(LENB(H35)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7537,26 +7614,24 @@
       <c r="AG35" s="16"/>
     </row>
     <row r="36" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="35" t="s">
-        <v>461</v>
-      </c>
-      <c r="E36" s="35"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
       <c r="F36" s="6" t="str">
         <f>IF(D36="","",IF(LENB(D36)/2&lt;=5,"OK","超過"))</f>
-        <v>OK</v>
+        <v/>
       </c>
       <c r="G36" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="H36" s="35" t="s">
+      <c r="H36" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="I36" s="35"/>
+      <c r="I36" s="28"/>
       <c r="J36" s="6" t="str">
         <f>IF(H36="","",IF(LENB(H36)/2&lt;=5,"OK","超過"))</f>
         <v>OK</v>
@@ -7589,8 +7664,8 @@
       <c r="AG36" s="16"/>
     </row>
     <row r="37" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
       <c r="C37" s="17" t="s">
         <v>6</v>
       </c>
@@ -7631,36 +7706,36 @@
       <c r="AG37" s="16"/>
     </row>
     <row r="39" spans="1:33" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="33" t="s">
+      <c r="A39" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="33" t="s">
+      <c r="B39" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32" t="s">
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32" t="s">
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="32" t="s">
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="32"/>
-      <c r="R39" s="32"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
       <c r="T39" s="14" t="s">
         <v>73</v>
       </c>
@@ -7679,15 +7754,15 @@
       <c r="AG39" s="12"/>
     </row>
     <row r="40" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="33"/>
-      <c r="B40" s="33"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
       <c r="C40" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="34" t="s">
+      <c r="D40" s="29" t="s">
         <v>469</v>
       </c>
-      <c r="E40" s="34"/>
+      <c r="E40" s="29"/>
       <c r="F40" s="6" t="str">
         <f>IF(D40="","待填",IF(ISNUMBER(SEARCH(".",D40)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7695,10 +7770,10 @@
       <c r="G40" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H40" s="34" t="s">
-        <v>477</v>
-      </c>
-      <c r="I40" s="34"/>
+      <c r="H40" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="I40" s="29"/>
       <c r="J40" s="6" t="str">
         <f>IF(H40="","待填",IF(ISNUMBER(SEARCH(".",H40)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7706,10 +7781,10 @@
       <c r="K40" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="L40" s="34" t="s">
+      <c r="L40" s="29" t="s">
         <v>469</v>
       </c>
-      <c r="M40" s="34"/>
+      <c r="M40" s="29"/>
       <c r="N40" s="6" t="str">
         <f>IF(L40="","待填",IF(ISNUMBER(SEARCH(".",L40)),"OK","記得加副檔名"))</f>
         <v>OK</v>
@@ -7736,15 +7811,15 @@
       <c r="AG40" s="16"/>
     </row>
     <row r="41" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="33"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="26"/>
       <c r="C41" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="E41" s="35"/>
+      <c r="D41" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="E41" s="28"/>
       <c r="F41" s="6" t="str">
         <f>IF(D41="","",IF(LENB(D41)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -7752,10 +7827,10 @@
       <c r="G41" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H41" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="I41" s="35"/>
+      <c r="H41" s="28" t="s">
+        <v>486</v>
+      </c>
+      <c r="I41" s="28"/>
       <c r="J41" s="6" t="str">
         <f>IF(H41="","",IF(LENB(H41)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -7763,10 +7838,10 @@
       <c r="K41" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="L41" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="M41" s="35"/>
+      <c r="L41" s="28" t="s">
+        <v>486</v>
+      </c>
+      <c r="M41" s="28"/>
       <c r="N41" s="6" t="str">
         <f>IF(L41="","",IF(LENB(L41)/2&lt;=7,"OK","超過"))</f>
         <v>OK</v>
@@ -7793,15 +7868,15 @@
       <c r="AG41" s="16"/>
     </row>
     <row r="42" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="33"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="26"/>
       <c r="C42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E42" s="35"/>
+      <c r="E42" s="28"/>
       <c r="F42" s="6" t="str">
         <f>IF(D42="","",IF(LENB(D42)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7809,10 +7884,10 @@
       <c r="G42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="H42" s="35" t="s">
+      <c r="H42" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="I42" s="35"/>
+      <c r="I42" s="28"/>
       <c r="J42" s="6" t="str">
         <f>IF(H42="","",IF(LENB(H42)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7820,10 +7895,10 @@
       <c r="K42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="L42" s="35" t="s">
+      <c r="L42" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="M42" s="35"/>
+      <c r="M42" s="28"/>
       <c r="N42" s="6" t="str">
         <f>IF(L42="","",IF(LENB(L42)/2&lt;=8,"OK","超過"))</f>
         <v>OK</v>
@@ -7850,8 +7925,8 @@
       <c r="AG42" s="16"/>
     </row>
     <row r="43" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="33"/>
-      <c r="B43" s="33"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="17" t="s">
         <v>6</v>
       </c>
@@ -7892,8 +7967,8 @@
       <c r="AG43" s="16"/>
     </row>
     <row r="44" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
-      <c r="B44" s="33"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
       <c r="C44" s="17" t="s">
         <v>6</v>
       </c>
@@ -7934,8 +8009,8 @@
       <c r="AG44" s="16"/>
     </row>
     <row r="45" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="26"/>
       <c r="C45" s="17" t="s">
         <v>6</v>
       </c>
@@ -8021,184 +8096,184 @@
       <c r="AG47" s="31"/>
     </row>
     <row r="48" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="B48" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="34" t="s">
         <v>114</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E48" s="30" t="s">
-        <v>480</v>
-      </c>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="23" t="s">
+      <c r="E48" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="34" t="s">
         <v>114</v>
       </c>
       <c r="I48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="J48" s="30" t="s">
+      <c r="J48" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="23" t="s">
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="34" t="s">
         <v>114</v>
       </c>
       <c r="N48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="O48" s="22" t="s">
+      <c r="O48" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="22"/>
-      <c r="R48" s="23" t="s">
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="34" t="s">
         <v>114</v>
       </c>
       <c r="S48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="T48" s="22" t="s">
+      <c r="T48" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="U48" s="22"/>
-      <c r="V48" s="22"/>
-      <c r="W48" s="22"/>
-      <c r="X48" s="22"/>
-      <c r="Y48" s="22"/>
-      <c r="Z48" s="23" t="s">
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="33"/>
+      <c r="Y48" s="33"/>
+      <c r="Z48" s="34" t="s">
         <v>114</v>
       </c>
       <c r="AA48" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="AB48" s="22" t="s">
+      <c r="AB48" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="AC48" s="22"/>
-      <c r="AD48" s="22"/>
-      <c r="AE48" s="22"/>
-      <c r="AF48" s="22"/>
-      <c r="AG48" s="22"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
+      <c r="AF48" s="33"/>
+      <c r="AG48" s="33"/>
     </row>
     <row r="49" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="23"/>
+      <c r="A49" s="39"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="34"/>
       <c r="D49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E49" s="30" t="s">
+      <c r="E49" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="23"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="34"/>
       <c r="I49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="J49" s="30" t="s">
-        <v>479</v>
-      </c>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="23"/>
+      <c r="J49" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="34"/>
       <c r="N49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="O49" s="22" t="s">
-        <v>479</v>
-      </c>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="22"/>
-      <c r="R49" s="23"/>
+      <c r="O49" s="33" t="s">
+        <v>478</v>
+      </c>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="34"/>
       <c r="S49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="T49" s="22" t="s">
-        <v>483</v>
-      </c>
-      <c r="U49" s="22"/>
-      <c r="V49" s="22"/>
-      <c r="W49" s="22"/>
-      <c r="X49" s="22"/>
-      <c r="Y49" s="22"/>
-      <c r="Z49" s="23"/>
+      <c r="T49" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="33"/>
+      <c r="Y49" s="33"/>
+      <c r="Z49" s="34"/>
       <c r="AA49" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="AB49" s="22" t="s">
+      <c r="AB49" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="AC49" s="22"/>
-      <c r="AD49" s="22"/>
-      <c r="AE49" s="22"/>
-      <c r="AF49" s="22"/>
-      <c r="AG49" s="22"/>
+      <c r="AC49" s="33"/>
+      <c r="AD49" s="33"/>
+      <c r="AE49" s="33"/>
+      <c r="AF49" s="33"/>
+      <c r="AG49" s="33"/>
     </row>
     <row r="50" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="24" t="s">
-        <v>478</v>
-      </c>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
+      <c r="A50" s="39"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
       <c r="G50" s="21">
         <f>IF(OR(C50="",C50="文案5字內"),"",LENB(C50)/2)</f>
         <v>3</v>
       </c>
-      <c r="H50" s="26" t="s">
-        <v>482</v>
-      </c>
-      <c r="I50" s="25"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="25"/>
+      <c r="H50" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
       <c r="L50" s="21">
         <f>IF(OR(H50="",H50="文案5字內"),"",LENB(H50)/2)</f>
         <v>2.5</v>
       </c>
-      <c r="M50" s="27" t="s">
-        <v>482</v>
-      </c>
-      <c r="N50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
+      <c r="M50" s="38" t="s">
+        <v>481</v>
+      </c>
+      <c r="N50" s="38"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="38"/>
       <c r="Q50" s="21">
         <f>IF(OR(M50="",M50="(需要再填即可)"),"",LENB(M50)/2)</f>
         <v>2.5</v>
       </c>
-      <c r="R50" s="27" t="s">
-        <v>481</v>
-      </c>
-      <c r="S50" s="27"/>
-      <c r="T50" s="27"/>
-      <c r="U50" s="27"/>
-      <c r="V50" s="27"/>
-      <c r="W50" s="27"/>
-      <c r="X50" s="27"/>
+      <c r="R50" s="38" t="s">
+        <v>480</v>
+      </c>
+      <c r="S50" s="38"/>
+      <c r="T50" s="38"/>
+      <c r="U50" s="38"/>
+      <c r="V50" s="38"/>
+      <c r="W50" s="38"/>
+      <c r="X50" s="38"/>
       <c r="Y50" s="21">
         <f>IF(OR(R50="",R50="(需要再填即可)"),"",LENB(R50)/2)</f>
         <v>2.5</v>
       </c>
-      <c r="Z50" s="27" t="s">
+      <c r="Z50" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="AA50" s="27"/>
-      <c r="AB50" s="27"/>
-      <c r="AC50" s="27"/>
-      <c r="AD50" s="27"/>
-      <c r="AE50" s="27"/>
-      <c r="AF50" s="27"/>
+      <c r="AA50" s="38"/>
+      <c r="AB50" s="38"/>
+      <c r="AC50" s="38"/>
+      <c r="AD50" s="38"/>
+      <c r="AE50" s="38"/>
+      <c r="AF50" s="38"/>
       <c r="AG50" s="21" t="str">
         <f>IF(OR(Z50="",Z50="(需要再填即可)"),"",LENB(Z50)/2)</f>
         <v/>
@@ -8208,6 +8283,94 @@
   <sheetProtection sheet="1" autoFilter="0"/>
   <autoFilter ref="A1:AG1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="112">
+    <mergeCell ref="T49:Y49"/>
+    <mergeCell ref="Z48:Z49"/>
+    <mergeCell ref="AB49:AG49"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="M50:P50"/>
+    <mergeCell ref="R50:X50"/>
+    <mergeCell ref="Z50:AF50"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="O49:Q49"/>
+    <mergeCell ref="R48:R49"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:L47"/>
+    <mergeCell ref="M47:Q47"/>
+    <mergeCell ref="R47:Y47"/>
+    <mergeCell ref="Z47:AG47"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="O48:Q48"/>
+    <mergeCell ref="T48:Y48"/>
+    <mergeCell ref="AB48:AG48"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="B39:B45"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="A31:A37"/>
+    <mergeCell ref="B31:B37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="C20:R20"/>
+    <mergeCell ref="A20:A29"/>
+    <mergeCell ref="B20:B29"/>
+    <mergeCell ref="D21:Q21"/>
+    <mergeCell ref="D22:Q22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="K23:R23"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="L24:Q24"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="L25:Q25"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="C11:R11"/>
+    <mergeCell ref="A11:A18"/>
+    <mergeCell ref="B11:B18"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="L15:Q15"/>
+    <mergeCell ref="L16:Q16"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="L18:Q18"/>
     <mergeCell ref="C1:R1"/>
     <mergeCell ref="T1:AG1"/>
     <mergeCell ref="A1:A2"/>
@@ -8232,94 +8395,6 @@
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="N6:Q6"/>
     <mergeCell ref="D7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C11:R11"/>
-    <mergeCell ref="A11:A18"/>
-    <mergeCell ref="B11:B18"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="L16:Q16"/>
-    <mergeCell ref="L17:Q17"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="C20:R20"/>
-    <mergeCell ref="A20:A29"/>
-    <mergeCell ref="B20:B29"/>
-    <mergeCell ref="D21:Q21"/>
-    <mergeCell ref="D22:Q22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="K23:R23"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="L24:Q24"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="L25:Q25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="A31:A37"/>
-    <mergeCell ref="B31:B37"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="B39:B45"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:L47"/>
-    <mergeCell ref="M47:Q47"/>
-    <mergeCell ref="R47:Y47"/>
-    <mergeCell ref="Z47:AG47"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="O48:Q48"/>
-    <mergeCell ref="T48:Y48"/>
-    <mergeCell ref="AB48:AG48"/>
-    <mergeCell ref="T49:Y49"/>
-    <mergeCell ref="Z48:Z49"/>
-    <mergeCell ref="AB49:AG49"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="M50:P50"/>
-    <mergeCell ref="R50:X50"/>
-    <mergeCell ref="Z50:AF50"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="M48:M49"/>
-    <mergeCell ref="O49:Q49"/>
-    <mergeCell ref="R48:R49"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="C50">
@@ -8783,12 +8858,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;L BODA 工單&amp;C MS Layout&amp;R 第 &amp;P / &amp;N 頁</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
